--- a/farmers-market-layout/sample/예시_참여명단.xlsx
+++ b/farmers-market-layout/sample/예시_참여명단.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -39,6 +39,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,9 +73,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -439,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -452,6 +460,7 @@
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,2006 +514,2067 @@
           <t>장소</t>
         </is>
       </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>전력(kW)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>강원</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>홍천군</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>햇살양봉원</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>홍길동</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>010-0000-0001</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>가공식품류</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>아카시아꿀, 야생화꿀, 로얄젤리</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>ㅇ</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>전북</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>무주군</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>산들식초방</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>김예시</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>010-0000-0002</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>가공식품류</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>감식초, 현미식초, 블루베리식초</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>경기</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>이천시</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>할매떡방앗간</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>이연습</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>010-0000-0003</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>가공식품류</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>인절미, 가래떡, 꿀떡</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>경북</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>안동시</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>다정한과</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>박샘플</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>010-0000-0004</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>가공식품류</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>약과, 유과, 강정</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>ㅇ</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>충남</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>논산시</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>초록잼공방</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>최가상</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>010-0000-0005</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>가공식품류</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>딸기잼, 무화과잼, 사과잼</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>전남</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>완도군</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>바다김공방</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>정테스트</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>010-0000-0006</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>가공식품류</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>김부각, 곱창김</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>양천</t>
         </is>
       </c>
+      <c r="K7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>충북</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>괴산군</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>고소한기름집</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>강예제</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>010-0000-0007</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>가공식품류</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>참기름, 들기름, 볶은참깨</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>ㅇ</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>경북</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>문경시</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>오미자마을</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>조보기</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>010-0000-0008</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>가공식품류</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>오미자청, 오미자 음료</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>경기</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>양평군</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>우리밀베이커리</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>윤견본</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>010-0000-0009</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>가공식품류</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>쌀식빵, 단호박 쌀빵, 쿠키</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>전북</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>전주시</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>전통식혜집</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>장시험</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>010-0000-0010</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>가공식품류</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>식혜, 수정과, 단호박식혜</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>ㅇ</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>강원</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>정선군</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>도라지명가</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>임모의</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>010-0000-0011</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>가공식품류</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>도라지청, 도라지정과</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>강원</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>평창군</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>산골두부</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>한가짜</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>010-0000-0012</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>가공식품류</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>두부, 순두부, 콩물</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>화랑대</t>
         </is>
       </c>
+      <c r="K13" s="3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>전남</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>구례군</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>꽃차정원</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>오예비</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>010-0000-0013</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>가공식품류</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>국화차, 메리골드차, 목련차</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>ㅇ</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>경북</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>상주시</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>감말랭이농원</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>서연습</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>010-0000-0014</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>가공식품류</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>감말랭이, 곶감</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>경북</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>청송군</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>사과향기농장</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>신샘플</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>010-0000-0015</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>과실류</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>사과(홍로, 부사), 사과즙</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>충북</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>영동군</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>언덕위포도원</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>권예시</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>010-0000-0016</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>과실류</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>샤인머스켓, 캠벨, 포도즙</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>ㅇ</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>충남</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>논산시</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>딸기네하우스</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>황가상</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>010-0000-0017</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>과실류</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>딸기, 딸기청</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>전북</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>고창군</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>블루베리언덕</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>안테스트</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>010-0000-0018</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>과실류</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>블루베리, 블루베리잼</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>양천</t>
         </is>
       </c>
+      <c r="K19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>전남</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>나주시</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>배꽃과수원</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>송예제</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>010-0000-0019</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>과실류</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>배, 배즙</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>ㅇ</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>창원시</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>단감마을</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>전보기</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>010-0000-0020</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>과실류</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>단감, 대봉감, 홍시</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>경기</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>이천시</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>복숭아밭</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>홍견본</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>010-0000-0021</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>과실류</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>복숭아, 자두</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>경북</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>영주시</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>사과나무집</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>김시험</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>010-0000-0022</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>과실류</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>사과, 사과칩, 사과즙</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>ㅇ</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>경기</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>남양주시</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>텃밭채소원</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>이모의</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>010-0000-0023</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>채소류</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>상추, 쌈채소, 토마토, 오이</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>강원</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>평창군</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>고랭지농원</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>박가짜</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>010-0000-0024</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>채소류</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>감자, 양배추, 배추</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>화랑대</t>
         </is>
       </c>
+      <c r="K25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>전남</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>해남군</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>햇고구마농장</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>최예비</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>010-0000-0025</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>채소류</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>고구마, 호박고구마, 단호박</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>ㅇ</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>창녕군</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>마늘양파농가</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>정연습</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>010-0000-0026</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>채소류</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>마늘, 양파, 대파</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>경기</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>가평군</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>허브정원</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>강샘플</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>010-0000-0027</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>채소류</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>바질, 로즈마리, 허브 모종</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>경북</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>고령군</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>숲속버섯농장</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>조예시</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>010-0000-0028</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>특용·임산물류</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>표고버섯, 느타리버섯</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>ㅇ</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>강원</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>인제군</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>산나물마을</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>윤가상</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>010-0000-0029</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>특용·임산물류</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>고사리, 취나물, 곤드레</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>충남</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>공주시</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>알밤농원</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>장테스트</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>010-0000-0030</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>특용·임산물류</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>알밤, 군밤</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>양천</t>
         </is>
       </c>
+      <c r="K31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>강원</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>영월군</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>산골약초원</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>임예제</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>010-0000-0031</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>특용·임산물류</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>더덕, 도라지, 황기</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>ㅇ</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>경기</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>가평군</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>잣나무숲</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>한보기</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>010-0000-0032</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>특용·임산물류</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>잣, 호두</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>경기</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>포천시</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>목장치즈공방</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>오견본</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>010-0000-0033</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>축산류</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>스트링치즈, 요거트, 우유</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>충북</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>음성군</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>행복한닭농장</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>서시험</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>010-0000-0034</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>축산류</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>유정란, 청계란</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>ㅇ</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>전북</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>무주군</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>벌꿀농원</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>신모의</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>010-0000-0035</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>축산류</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>벌꿀, 화분, 프로폴리스</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>충남</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>홍성군</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>바닷가젓갈</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>권가짜</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>010-0000-0036</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>수산물류</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>새우젓, 명란젓, 멸치액젓</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>남해군</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>남해건어물</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>황예비</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>010-0000-0037</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>수산물류</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>멸치, 다시마, 미역</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>ㅇ</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>전북</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>순창군</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>장독대된장</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>안연습</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>010-0000-0038</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>반찬·장류</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>된장, 고추장, 청국장</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>전남</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>해남군</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>엄마손김치</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>송샘플</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>010-0000-0039</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>반찬·장류</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>배추김치, 깍두기, 갓김치</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>전남</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>영광군</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>들녘잡곡</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>전예시</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>010-0000-0040</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>양곡류</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>현미, 찹쌀, 서리태, 귀리</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>ㅇ</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>뚝섬</t>
-        </is>
-      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>뚝섬</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
